--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.3209888532311</v>
+        <v>9.152160688650055</v>
       </c>
       <c r="D2" t="n">
-        <v>54.22114285773176</v>
+        <v>8.810935714381412</v>
       </c>
       <c r="E2" t="n">
-        <v>14.66934447183536</v>
+        <v>2.383768476673246</v>
       </c>
       <c r="F2" t="n">
-        <v>15.68436687327964</v>
+        <v>2.548709616907941</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.46904934628814</v>
+        <v>6.088720518771822</v>
       </c>
       <c r="D3" t="n">
-        <v>36.80810004437964</v>
+        <v>5.981316257211692</v>
       </c>
       <c r="E3" t="n">
-        <v>14.66934447183536</v>
+        <v>2.383768476673246</v>
       </c>
       <c r="F3" t="n">
-        <v>15.68436687327964</v>
+        <v>2.548709616907941</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>73.3866552359078</v>
+        <v>11.92533147583502</v>
       </c>
       <c r="D4" t="n">
-        <v>75.1724466234384</v>
+        <v>12.21552257630874</v>
       </c>
       <c r="E4" t="n">
-        <v>14.66934447183536</v>
+        <v>2.383768476673246</v>
       </c>
       <c r="F4" t="n">
-        <v>15.68436687327964</v>
+        <v>2.548709616907941</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
